--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511189</v>
+        <v>113511183</v>
       </c>
       <c r="B2" t="n">
-        <v>90370</v>
+        <v>90377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552745</v>
+        <v>552613</v>
       </c>
       <c r="R2" t="n">
-        <v>7036698</v>
+        <v>7036803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511192</v>
+        <v>113511188</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>97385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552790</v>
+        <v>552708</v>
       </c>
       <c r="R3" t="n">
-        <v>7036593</v>
+        <v>7036722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511174</v>
+        <v>113511190</v>
       </c>
       <c r="B4" t="n">
-        <v>79228</v>
+        <v>81913</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552825</v>
+        <v>552762</v>
       </c>
       <c r="R4" t="n">
-        <v>7037030</v>
+        <v>7036688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>113511185</v>
       </c>
       <c r="B5" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>113511181</v>
       </c>
       <c r="B6" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511190</v>
+        <v>113511182</v>
       </c>
       <c r="B7" t="n">
-        <v>81906</v>
+        <v>90092</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552762</v>
+        <v>552595</v>
       </c>
       <c r="R7" t="n">
-        <v>7036688</v>
+        <v>7036826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511182</v>
+        <v>113511174</v>
       </c>
       <c r="B8" t="n">
-        <v>90085</v>
+        <v>79235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552595</v>
+        <v>552825</v>
       </c>
       <c r="R8" t="n">
-        <v>7036826</v>
+        <v>7037030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511183</v>
+        <v>113511192</v>
       </c>
       <c r="B9" t="n">
-        <v>90370</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552613</v>
+        <v>552790</v>
       </c>
       <c r="R9" t="n">
-        <v>7036803</v>
+        <v>7036593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>113511180</v>
       </c>
       <c r="B10" t="n">
-        <v>93789</v>
+        <v>93796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511188</v>
+        <v>113511189</v>
       </c>
       <c r="B11" t="n">
-        <v>97378</v>
+        <v>90377</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552708</v>
+        <v>552745</v>
       </c>
       <c r="R11" t="n">
-        <v>7036722</v>
+        <v>7036698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511181</v>
+        <v>113511182</v>
       </c>
       <c r="B6" t="n">
-        <v>56780</v>
+        <v>90092</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,42 +1123,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552548</v>
+        <v>552595</v>
       </c>
       <c r="R6" t="n">
-        <v>7036902</v>
+        <v>7036826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511182</v>
+        <v>113511174</v>
       </c>
       <c r="B7" t="n">
-        <v>90092</v>
+        <v>79235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552595</v>
+        <v>552825</v>
       </c>
       <c r="R7" t="n">
-        <v>7036826</v>
+        <v>7037030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511174</v>
+        <v>113511181</v>
       </c>
       <c r="B8" t="n">
-        <v>79235</v>
+        <v>56780</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,34 +1335,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552825</v>
+        <v>552548</v>
       </c>
       <c r="R8" t="n">
-        <v>7037030</v>
+        <v>7036902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511182</v>
+        <v>113511181</v>
       </c>
       <c r="B6" t="n">
-        <v>90092</v>
+        <v>56780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,34 +1123,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552595</v>
+        <v>552548</v>
       </c>
       <c r="R6" t="n">
-        <v>7036826</v>
+        <v>7036902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511174</v>
+        <v>113511182</v>
       </c>
       <c r="B7" t="n">
-        <v>79235</v>
+        <v>90092</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552825</v>
+        <v>552595</v>
       </c>
       <c r="R7" t="n">
-        <v>7037030</v>
+        <v>7036826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511181</v>
+        <v>113511174</v>
       </c>
       <c r="B8" t="n">
-        <v>56780</v>
+        <v>79235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,42 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552548</v>
+        <v>552825</v>
       </c>
       <c r="R8" t="n">
-        <v>7036902</v>
+        <v>7037030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511181</v>
+        <v>113511174</v>
       </c>
       <c r="B6" t="n">
-        <v>56780</v>
+        <v>79235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,42 +1123,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552548</v>
+        <v>552825</v>
       </c>
       <c r="R6" t="n">
-        <v>7036902</v>
+        <v>7037030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511182</v>
+        <v>113511181</v>
       </c>
       <c r="B7" t="n">
-        <v>90092</v>
+        <v>56780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,34 +1229,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552595</v>
+        <v>552548</v>
       </c>
       <c r="R7" t="n">
-        <v>7036826</v>
+        <v>7036902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511174</v>
+        <v>113511182</v>
       </c>
       <c r="B8" t="n">
-        <v>79235</v>
+        <v>90092</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552825</v>
+        <v>552595</v>
       </c>
       <c r="R8" t="n">
-        <v>7037030</v>
+        <v>7036826</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511183</v>
+        <v>113511180</v>
       </c>
       <c r="B2" t="n">
-        <v>90377</v>
+        <v>93801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552613</v>
+        <v>552605</v>
       </c>
       <c r="R2" t="n">
-        <v>7036803</v>
+        <v>7036980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511188</v>
+        <v>113511190</v>
       </c>
       <c r="B3" t="n">
-        <v>97385</v>
+        <v>81916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552708</v>
+        <v>552762</v>
       </c>
       <c r="R3" t="n">
-        <v>7036722</v>
+        <v>7036688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511190</v>
+        <v>113511182</v>
       </c>
       <c r="B4" t="n">
-        <v>81913</v>
+        <v>90095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552762</v>
+        <v>552595</v>
       </c>
       <c r="R4" t="n">
-        <v>7036688</v>
+        <v>7036826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511185</v>
+        <v>113511183</v>
       </c>
       <c r="B5" t="n">
-        <v>56780</v>
+        <v>90380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,42 +1010,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552633</v>
+        <v>552613</v>
       </c>
       <c r="R5" t="n">
-        <v>7036759</v>
+        <v>7036803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511174</v>
+        <v>113511192</v>
       </c>
       <c r="B6" t="n">
-        <v>79235</v>
+        <v>78173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552825</v>
+        <v>552790</v>
       </c>
       <c r="R6" t="n">
-        <v>7037030</v>
+        <v>7036593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511181</v>
+        <v>113511185</v>
       </c>
       <c r="B7" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552548</v>
+        <v>552633</v>
       </c>
       <c r="R7" t="n">
-        <v>7036902</v>
+        <v>7036759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511182</v>
+        <v>113511189</v>
       </c>
       <c r="B8" t="n">
-        <v>90092</v>
+        <v>90380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552595</v>
+        <v>552745</v>
       </c>
       <c r="R8" t="n">
-        <v>7036826</v>
+        <v>7036698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511192</v>
+        <v>113511188</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>97390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,25 +1438,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552790</v>
+        <v>552708</v>
       </c>
       <c r="R9" t="n">
-        <v>7036593</v>
+        <v>7036722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511180</v>
+        <v>113511174</v>
       </c>
       <c r="B10" t="n">
-        <v>93796</v>
+        <v>79237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,25 +1544,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552605</v>
+        <v>552825</v>
       </c>
       <c r="R10" t="n">
-        <v>7036980</v>
+        <v>7037030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1646,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511189</v>
+        <v>113511181</v>
       </c>
       <c r="B11" t="n">
-        <v>90377</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,34 +1654,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552745</v>
+        <v>552548</v>
       </c>
       <c r="R11" t="n">
-        <v>7036698</v>
+        <v>7036902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511180</v>
+        <v>113511188</v>
       </c>
       <c r="B2" t="n">
-        <v>93801</v>
+        <v>97418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552605</v>
+        <v>552708</v>
       </c>
       <c r="R2" t="n">
-        <v>7036980</v>
+        <v>7036722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511190</v>
+        <v>113511174</v>
       </c>
       <c r="B3" t="n">
-        <v>81916</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552762</v>
+        <v>552825</v>
       </c>
       <c r="R3" t="n">
-        <v>7036688</v>
+        <v>7037030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511182</v>
+        <v>113511185</v>
       </c>
       <c r="B4" t="n">
-        <v>90095</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +903,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552595</v>
+        <v>552633</v>
       </c>
       <c r="R4" t="n">
-        <v>7036826</v>
+        <v>7036759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511183</v>
+        <v>113511182</v>
       </c>
       <c r="B5" t="n">
-        <v>90380</v>
+        <v>90126</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552613</v>
+        <v>552595</v>
       </c>
       <c r="R5" t="n">
-        <v>7036803</v>
+        <v>7036826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511192</v>
+        <v>113511190</v>
       </c>
       <c r="B6" t="n">
-        <v>78173</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552790</v>
+        <v>552762</v>
       </c>
       <c r="R6" t="n">
-        <v>7036593</v>
+        <v>7036688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511185</v>
+        <v>113511180</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>93829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,46 +1225,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552633</v>
+        <v>552605</v>
       </c>
       <c r="R7" t="n">
-        <v>7036759</v>
+        <v>7036980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1297,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511189</v>
+        <v>113511183</v>
       </c>
       <c r="B8" t="n">
-        <v>90380</v>
+        <v>90411</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552745</v>
+        <v>552613</v>
       </c>
       <c r="R8" t="n">
-        <v>7036698</v>
+        <v>7036803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511188</v>
+        <v>113511189</v>
       </c>
       <c r="B9" t="n">
-        <v>97390</v>
+        <v>90411</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1438,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552708</v>
+        <v>552745</v>
       </c>
       <c r="R9" t="n">
-        <v>7036722</v>
+        <v>7036698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511174</v>
+        <v>113511181</v>
       </c>
       <c r="B10" t="n">
-        <v>79237</v>
+        <v>56810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,34 +1548,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552825</v>
+        <v>552548</v>
       </c>
       <c r="R10" t="n">
-        <v>7037030</v>
+        <v>7036902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511181</v>
+        <v>113511192</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>78201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,42 +1662,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552548</v>
+        <v>552790</v>
       </c>
       <c r="R11" t="n">
-        <v>7036902</v>
+        <v>7036593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511188</v>
+        <v>113511174</v>
       </c>
       <c r="B2" t="n">
-        <v>97418</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552708</v>
+        <v>552825</v>
       </c>
       <c r="R2" t="n">
-        <v>7036722</v>
+        <v>7037030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511174</v>
+        <v>113511185</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552825</v>
+        <v>552633</v>
       </c>
       <c r="R3" t="n">
-        <v>7037030</v>
+        <v>7036759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511185</v>
+        <v>113511188</v>
       </c>
       <c r="B4" t="n">
-        <v>56810</v>
+        <v>97418</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,46 +907,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552633</v>
+        <v>552708</v>
       </c>
       <c r="R4" t="n">
-        <v>7036759</v>
+        <v>7036722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511174</v>
+        <v>113511181</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>56810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552825</v>
+        <v>552548</v>
       </c>
       <c r="R2" t="n">
-        <v>7037030</v>
+        <v>7036902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511185</v>
+        <v>113511182</v>
       </c>
       <c r="B3" t="n">
-        <v>56810</v>
+        <v>90127</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,42 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552633</v>
+        <v>552595</v>
       </c>
       <c r="R3" t="n">
-        <v>7036759</v>
+        <v>7036826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511188</v>
+        <v>113511189</v>
       </c>
       <c r="B4" t="n">
-        <v>97418</v>
+        <v>90412</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552708</v>
+        <v>552745</v>
       </c>
       <c r="R4" t="n">
-        <v>7036722</v>
+        <v>7036698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511182</v>
+        <v>113511180</v>
       </c>
       <c r="B5" t="n">
-        <v>90126</v>
+        <v>93829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552595</v>
+        <v>552605</v>
       </c>
       <c r="R5" t="n">
-        <v>7036826</v>
+        <v>7036980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1085,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511190</v>
+        <v>113511192</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552762</v>
+        <v>552790</v>
       </c>
       <c r="R6" t="n">
-        <v>7036688</v>
+        <v>7036593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511180</v>
+        <v>113511183</v>
       </c>
       <c r="B7" t="n">
-        <v>93829</v>
+        <v>90412</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552605</v>
+        <v>552613</v>
       </c>
       <c r="R7" t="n">
-        <v>7036980</v>
+        <v>7036803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1298,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511183</v>
+        <v>113511185</v>
       </c>
       <c r="B8" t="n">
-        <v>90411</v>
+        <v>56810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,34 +1336,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552613</v>
+        <v>552633</v>
       </c>
       <c r="R8" t="n">
-        <v>7036803</v>
+        <v>7036759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511189</v>
+        <v>113511190</v>
       </c>
       <c r="B9" t="n">
-        <v>90411</v>
+        <v>81944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552745</v>
+        <v>552762</v>
       </c>
       <c r="R9" t="n">
-        <v>7036698</v>
+        <v>7036688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511181</v>
+        <v>113511174</v>
       </c>
       <c r="B10" t="n">
-        <v>56810</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,42 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552548</v>
+        <v>552825</v>
       </c>
       <c r="R10" t="n">
-        <v>7036902</v>
+        <v>7037030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511192</v>
+        <v>113511188</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>97418</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552790</v>
+        <v>552708</v>
       </c>
       <c r="R11" t="n">
-        <v>7036593</v>
+        <v>7036722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511181</v>
+        <v>113511192</v>
       </c>
       <c r="B2" t="n">
-        <v>56810</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552548</v>
+        <v>552790</v>
       </c>
       <c r="R2" t="n">
-        <v>7036902</v>
+        <v>7036593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511182</v>
+        <v>113511183</v>
       </c>
       <c r="B3" t="n">
-        <v>90127</v>
+        <v>90416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552595</v>
+        <v>552613</v>
       </c>
       <c r="R3" t="n">
-        <v>7036826</v>
+        <v>7036803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511189</v>
+        <v>113511185</v>
       </c>
       <c r="B4" t="n">
-        <v>90412</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,34 +903,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552745</v>
+        <v>552633</v>
       </c>
       <c r="R4" t="n">
-        <v>7036698</v>
+        <v>7036759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511180</v>
+        <v>113511181</v>
       </c>
       <c r="B5" t="n">
-        <v>93829</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,38 +1013,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552605</v>
+        <v>552548</v>
       </c>
       <c r="R5" t="n">
-        <v>7036980</v>
+        <v>7036902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511192</v>
+        <v>113511190</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552790</v>
+        <v>552762</v>
       </c>
       <c r="R6" t="n">
-        <v>7036593</v>
+        <v>7036688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511183</v>
+        <v>113511180</v>
       </c>
       <c r="B7" t="n">
-        <v>90412</v>
+        <v>93833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1233,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552613</v>
+        <v>552605</v>
       </c>
       <c r="R7" t="n">
-        <v>7036803</v>
+        <v>7036980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1305,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511185</v>
+        <v>113511188</v>
       </c>
       <c r="B8" t="n">
-        <v>56810</v>
+        <v>97422</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,46 +1340,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552633</v>
+        <v>552708</v>
       </c>
       <c r="R8" t="n">
-        <v>7036759</v>
+        <v>7036722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511190</v>
+        <v>113511174</v>
       </c>
       <c r="B9" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552762</v>
+        <v>552825</v>
       </c>
       <c r="R9" t="n">
-        <v>7036688</v>
+        <v>7037030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511174</v>
+        <v>113511182</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>90131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552825</v>
+        <v>552595</v>
       </c>
       <c r="R10" t="n">
-        <v>7037030</v>
+        <v>7036826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511188</v>
+        <v>113511189</v>
       </c>
       <c r="B11" t="n">
-        <v>97418</v>
+        <v>90416</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552708</v>
+        <v>552745</v>
       </c>
       <c r="R11" t="n">
-        <v>7036722</v>
+        <v>7036698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511192</v>
+        <v>113511189</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>90416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552790</v>
+        <v>552745</v>
       </c>
       <c r="R2" t="n">
-        <v>7036593</v>
+        <v>7036698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511183</v>
+        <v>113511182</v>
       </c>
       <c r="B3" t="n">
-        <v>90416</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552613</v>
+        <v>552595</v>
       </c>
       <c r="R3" t="n">
-        <v>7036803</v>
+        <v>7036826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511185</v>
+        <v>113511180</v>
       </c>
       <c r="B4" t="n">
-        <v>56810</v>
+        <v>93833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,46 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552633</v>
+        <v>552605</v>
       </c>
       <c r="R4" t="n">
-        <v>7036759</v>
+        <v>7036980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511181</v>
+        <v>113511188</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>97422</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,46 +1006,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552548</v>
+        <v>552708</v>
       </c>
       <c r="R5" t="n">
-        <v>7036902</v>
+        <v>7036722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511190</v>
+        <v>113511174</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552762</v>
+        <v>552825</v>
       </c>
       <c r="R6" t="n">
-        <v>7036688</v>
+        <v>7037030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511180</v>
+        <v>113511192</v>
       </c>
       <c r="B7" t="n">
-        <v>93833</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552605</v>
+        <v>552790</v>
       </c>
       <c r="R7" t="n">
-        <v>7036980</v>
+        <v>7036593</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1290,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511188</v>
+        <v>113511185</v>
       </c>
       <c r="B8" t="n">
-        <v>97422</v>
+        <v>56810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,38 +1324,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552708</v>
+        <v>552633</v>
       </c>
       <c r="R8" t="n">
-        <v>7036722</v>
+        <v>7036759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511174</v>
+        <v>113511190</v>
       </c>
       <c r="B9" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552825</v>
+        <v>552762</v>
       </c>
       <c r="R9" t="n">
-        <v>7037030</v>
+        <v>7036688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511182</v>
+        <v>113511181</v>
       </c>
       <c r="B10" t="n">
-        <v>90131</v>
+        <v>56810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,34 +1548,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552595</v>
+        <v>552548</v>
       </c>
       <c r="R10" t="n">
-        <v>7036826</v>
+        <v>7036902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511189</v>
+        <v>113511183</v>
       </c>
       <c r="B11" t="n">
         <v>90416</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552745</v>
+        <v>552613</v>
       </c>
       <c r="R11" t="n">
-        <v>7036698</v>
+        <v>7036803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511189</v>
+        <v>113511183</v>
       </c>
       <c r="B2" t="n">
         <v>90416</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552745</v>
+        <v>552613</v>
       </c>
       <c r="R2" t="n">
-        <v>7036698</v>
+        <v>7036803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511182</v>
+        <v>113511192</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552595</v>
+        <v>552790</v>
       </c>
       <c r="R3" t="n">
-        <v>7036826</v>
+        <v>7036593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511180</v>
+        <v>113511185</v>
       </c>
       <c r="B4" t="n">
-        <v>93833</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552605</v>
+        <v>552633</v>
       </c>
       <c r="R4" t="n">
-        <v>7036980</v>
+        <v>7036759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511188</v>
+        <v>113511190</v>
       </c>
       <c r="B5" t="n">
-        <v>97422</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552708</v>
+        <v>552762</v>
       </c>
       <c r="R5" t="n">
-        <v>7036722</v>
+        <v>7036688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511174</v>
+        <v>113511180</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>93833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552825</v>
+        <v>552605</v>
       </c>
       <c r="R6" t="n">
-        <v>7037030</v>
+        <v>7036980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1191,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511192</v>
+        <v>113511188</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>97422</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552790</v>
+        <v>552708</v>
       </c>
       <c r="R7" t="n">
-        <v>7036593</v>
+        <v>7036722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511185</v>
+        <v>113511174</v>
       </c>
       <c r="B8" t="n">
-        <v>56810</v>
+        <v>79265</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,42 +1336,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552633</v>
+        <v>552825</v>
       </c>
       <c r="R8" t="n">
-        <v>7036759</v>
+        <v>7037030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511190</v>
+        <v>113511181</v>
       </c>
       <c r="B9" t="n">
-        <v>81944</v>
+        <v>56810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,34 +1442,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552762</v>
+        <v>552548</v>
       </c>
       <c r="R9" t="n">
-        <v>7036688</v>
+        <v>7036902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511181</v>
+        <v>113511189</v>
       </c>
       <c r="B10" t="n">
-        <v>56810</v>
+        <v>90416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,42 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552548</v>
+        <v>552745</v>
       </c>
       <c r="R10" t="n">
-        <v>7036902</v>
+        <v>7036698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511183</v>
+        <v>113511182</v>
       </c>
       <c r="B11" t="n">
-        <v>90416</v>
+        <v>90131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552613</v>
+        <v>552595</v>
       </c>
       <c r="R11" t="n">
-        <v>7036803</v>
+        <v>7036826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511183</v>
+        <v>113511190</v>
       </c>
       <c r="B2" t="n">
-        <v>90416</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552613</v>
+        <v>552762</v>
       </c>
       <c r="R2" t="n">
-        <v>7036803</v>
+        <v>7036688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511192</v>
+        <v>113511183</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>90416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552790</v>
+        <v>552613</v>
       </c>
       <c r="R3" t="n">
-        <v>7036593</v>
+        <v>7036803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511185</v>
+        <v>113511180</v>
       </c>
       <c r="B4" t="n">
-        <v>56810</v>
+        <v>93833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,46 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552633</v>
+        <v>552605</v>
       </c>
       <c r="R4" t="n">
-        <v>7036759</v>
+        <v>7036980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511190</v>
+        <v>113511192</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552762</v>
+        <v>552790</v>
       </c>
       <c r="R5" t="n">
-        <v>7036688</v>
+        <v>7036593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511180</v>
+        <v>113511189</v>
       </c>
       <c r="B6" t="n">
-        <v>93833</v>
+        <v>90416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552605</v>
+        <v>552745</v>
       </c>
       <c r="R6" t="n">
-        <v>7036980</v>
+        <v>7036698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1184,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511188</v>
+        <v>113511182</v>
       </c>
       <c r="B7" t="n">
-        <v>97422</v>
+        <v>90131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552708</v>
+        <v>552595</v>
       </c>
       <c r="R7" t="n">
-        <v>7036722</v>
+        <v>7036826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511174</v>
+        <v>113511185</v>
       </c>
       <c r="B8" t="n">
-        <v>79265</v>
+        <v>56810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,34 +1328,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552825</v>
+        <v>552633</v>
       </c>
       <c r="R8" t="n">
-        <v>7037030</v>
+        <v>7036759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511181</v>
+        <v>113511174</v>
       </c>
       <c r="B9" t="n">
-        <v>56810</v>
+        <v>79265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,42 +1442,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552548</v>
+        <v>552825</v>
       </c>
       <c r="R9" t="n">
-        <v>7036902</v>
+        <v>7037030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511189</v>
+        <v>113511188</v>
       </c>
       <c r="B10" t="n">
-        <v>90416</v>
+        <v>97422</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1544,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552745</v>
+        <v>552708</v>
       </c>
       <c r="R10" t="n">
-        <v>7036698</v>
+        <v>7036722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511182</v>
+        <v>113511181</v>
       </c>
       <c r="B11" t="n">
-        <v>90131</v>
+        <v>56810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,34 +1654,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552595</v>
+        <v>552548</v>
       </c>
       <c r="R11" t="n">
-        <v>7036826</v>
+        <v>7036902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511189</v>
+        <v>113511182</v>
       </c>
       <c r="B6" t="n">
-        <v>90416</v>
+        <v>90131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552745</v>
+        <v>552595</v>
       </c>
       <c r="R6" t="n">
-        <v>7036698</v>
+        <v>7036826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511182</v>
+        <v>113511189</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>90416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552595</v>
+        <v>552745</v>
       </c>
       <c r="R7" t="n">
-        <v>7036826</v>
+        <v>7036698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511190</v>
+        <v>113511183</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>90416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552762</v>
+        <v>552613</v>
       </c>
       <c r="R2" t="n">
-        <v>7036688</v>
+        <v>7036803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511183</v>
+        <v>113511182</v>
       </c>
       <c r="B3" t="n">
-        <v>90416</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552613</v>
+        <v>552595</v>
       </c>
       <c r="R3" t="n">
-        <v>7036803</v>
+        <v>7036826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511180</v>
+        <v>113511181</v>
       </c>
       <c r="B4" t="n">
-        <v>93833</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552605</v>
+        <v>552548</v>
       </c>
       <c r="R4" t="n">
-        <v>7036980</v>
+        <v>7036902</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511182</v>
+        <v>113511185</v>
       </c>
       <c r="B6" t="n">
-        <v>90131</v>
+        <v>56810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,34 +1123,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552595</v>
+        <v>552633</v>
       </c>
       <c r="R6" t="n">
-        <v>7036826</v>
+        <v>7036759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511189</v>
+        <v>113511174</v>
       </c>
       <c r="B7" t="n">
-        <v>90416</v>
+        <v>79265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552745</v>
+        <v>552825</v>
       </c>
       <c r="R7" t="n">
-        <v>7036698</v>
+        <v>7037030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511185</v>
+        <v>113511180</v>
       </c>
       <c r="B8" t="n">
-        <v>56810</v>
+        <v>93833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,46 +1339,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552633</v>
+        <v>552605</v>
       </c>
       <c r="R8" t="n">
-        <v>7036759</v>
+        <v>7036980</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1426,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511174</v>
+        <v>113511188</v>
       </c>
       <c r="B9" t="n">
-        <v>79265</v>
+        <v>97422</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552825</v>
+        <v>552708</v>
       </c>
       <c r="R9" t="n">
-        <v>7037030</v>
+        <v>7036722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511188</v>
+        <v>113511189</v>
       </c>
       <c r="B10" t="n">
-        <v>97422</v>
+        <v>90416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552708</v>
+        <v>552745</v>
       </c>
       <c r="R10" t="n">
-        <v>7036722</v>
+        <v>7036698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113511181</v>
+        <v>113511190</v>
       </c>
       <c r="B11" t="n">
-        <v>56810</v>
+        <v>81944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,42 +1662,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552548</v>
+        <v>552762</v>
       </c>
       <c r="R11" t="n">
-        <v>7036902</v>
+        <v>7036688</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113511183</v>
       </c>
       <c r="B2" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113511190</v>
+        <v>113511189</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552762</v>
+        <v>552745</v>
       </c>
       <c r="R3" t="n">
-        <v>7036688</v>
+        <v>7036697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511188</v>
+        <v>113511182</v>
       </c>
       <c r="B4" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552708</v>
+        <v>552595</v>
       </c>
       <c r="R4" t="n">
-        <v>7036722</v>
+        <v>7036826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511182</v>
+        <v>113511170</v>
       </c>
       <c r="B5" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552595</v>
+        <v>552869</v>
       </c>
       <c r="R5" t="n">
-        <v>7036826</v>
+        <v>7037041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511189</v>
+        <v>113511190</v>
       </c>
       <c r="B6" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552745</v>
+        <v>552762</v>
       </c>
       <c r="R6" t="n">
-        <v>7036697</v>
+        <v>7036688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511192</v>
+        <v>113511180</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552790</v>
+        <v>552605</v>
       </c>
       <c r="R7" t="n">
-        <v>7036593</v>
+        <v>7036980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,37 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511180</v>
+        <v>113511192</v>
       </c>
       <c r="B8" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552605</v>
+        <v>552790</v>
       </c>
       <c r="R8" t="n">
-        <v>7036980</v>
+        <v>7036593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1361,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1418,15 +1383,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113511185</v>
+        <v>113511169</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,42 +1394,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552633</v>
+        <v>552867</v>
       </c>
       <c r="R9" t="n">
-        <v>7036759</v>
+        <v>7037028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113511181</v>
+        <v>113511174</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,42 +1495,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552548</v>
+        <v>552825</v>
       </c>
       <c r="R10" t="n">
-        <v>7036902</v>
+        <v>7037031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,6 +1578,426 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113511173</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552825</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037034</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113511181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552548</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7036902</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113511185</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552633</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7036759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113511188</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552708</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7036722</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 62992-2023 artfynd.xlsx
+++ b/artfynd/A 62992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511189</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511182</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511170</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511190</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511180</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511192</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511169</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511174</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511173</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511181</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511185</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,8 +2067,28 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511188</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>